--- a/VAV Schedules (Linked to AHU Psych).xlsx
+++ b/VAV Schedules (Linked to AHU Psych).xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git Projects\PsychroCalc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FD6E44-7B64-42BB-AE8F-95659FC6F846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608EB19D-9E66-4804-8A5A-776C4A558557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{86A44EAC-CB69-49D3-BD32-58BB1DF133E4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{255CF481-9D8E-4326-9236-7F323F1440D3}"/>
   </bookViews>
   <sheets>
     <sheet name="AH1_VAV_SCHEDULES" sheetId="2" r:id="rId1"/>
@@ -57,10 +57,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={57AE57DA-4710-4B7A-B7AD-D13E0998DF44}</author>
+    <author>tc={1CC13B16-4C20-403A-AC1C-35A7DA0101B2}</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{57AE57DA-4710-4B7A-B7AD-D13E0998DF44}">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{1CC13B16-4C20-403A-AC1C-35A7DA0101B2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>ZONE</t>
   </si>
@@ -169,7 +169,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,7 +186,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -198,6 +197,12 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -300,30 +305,30 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{EC4E104E-B976-44CF-87BD-5096FF453953}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{2BEF4A22-EF41-4147-BABC-84CF8CD79B60}"/>
   </cellStyles>
   <dxfs count="44">
     <dxf>
@@ -343,13 +348,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -383,6 +381,581 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
           <color indexed="64"/>
         </left>
         <right/>
@@ -412,45 +985,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -486,45 +1020,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -560,45 +1055,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -635,24 +1091,20 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -708,46 +1160,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -782,45 +1194,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -855,45 +1228,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -928,45 +1262,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1001,45 +1296,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1074,45 +1330,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1147,45 +1364,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1220,45 +1398,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1293,45 +1432,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1361,50 +1461,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1439,25 +1501,20 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -1478,7 +1535,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1513,50 +1569,9 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1570,199 +1585,11 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1770,6 +1597,52 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1839,7 +1712,7 @@
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001080000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{433A2705-7D24-45C4-BD22-182E6DDC0EDC}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1928,19 +1801,19 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
       <sheetData sheetId="14">
         <row r="9">
           <cell r="C9">
@@ -2016,66 +1889,66 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Rushikesh Patil" id="{15E600FB-89F4-415C-AD33-71A53D824548}" userId="S::rdp352@nyu.edu::e20300c4-5136-4b7e-8e5f-b0b27a3a3193" providerId="AD"/>
+  <person displayName="Rushikesh Patil" id="{5E313C26-8C82-4988-B6C0-99D50F1B0F4E}" userId="S::rdp352@nyu.edu::e20300c4-5136-4b7e-8e5f-b0b27a3a3193" providerId="AD"/>
 </personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA482A59-E5AB-4FCC-BFFD-84D5F77E8130}" name="AH1_VAV_table" displayName="AH1_VAV_table" ref="A4:S17" totalsRowCount="1" headerRowDxfId="43" dataDxfId="41" totalsRowDxfId="39" headerRowBorderDxfId="42" tableBorderDxfId="40" totalsRowBorderDxfId="38">
-  <autoFilter ref="A4:S16" xr:uid="{13D566E9-CE9D-4920-9557-440C01DE1A40}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0225CE1B-3CC1-45C3-BD85-3A7AD65EB02C}" name="AH1_VAV_table" displayName="AH1_VAV_table" ref="A4:S7" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42" totalsRowDxfId="41" headerRowBorderDxfId="39" tableBorderDxfId="40" totalsRowBorderDxfId="38">
+  <autoFilter ref="A4:S6" xr:uid="{13D566E9-CE9D-4920-9557-440C01DE1A40}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{84D66386-81A3-4B55-9F94-D9C375812C2F}" name="ZONE" totalsRowLabel="Total" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{077E2DB6-686D-42EC-99AF-96BC75E9B6B2}" name="BASIS OF DESIGN _x000a_MANUFACTURER" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{1D37524C-2DCB-42E3-BA3A-3DD88F474083}" name="DESCRIPTION" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="18" xr3:uid="{289237CB-6DFB-474C-AD8C-41A0450DDC5E}" name="MIN VAV_x000a_(CFM)" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="1" xr3:uid="{BDD53485-BD27-4C42-BCE6-4A791F13693B}" name="ZONE" totalsRowLabel="Total" dataDxfId="37" totalsRowDxfId="18" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{87D39EA5-B0A4-4FD0-8141-476AD3CFAF7B}" name="BASIS OF DESIGN _x000a_MANUFACTURER" dataDxfId="36" totalsRowDxfId="17" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{1F4067F0-0958-440B-887B-D04A70FA8DD0}" name="DESCRIPTION" dataDxfId="35" totalsRowDxfId="16" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="18" xr3:uid="{D0A6DBCB-AF09-4AFE-AC42-84877BED6114}" name="MIN VAV_x000a_(CFM)" dataDxfId="34" totalsRowDxfId="15" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MIN SA(CFM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{AE45AE68-5DF3-4920-B054-0AC78AAC6142}" name="MAX VAV_x000a_(CFM)" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="20" xr3:uid="{352CF6FC-C856-4BE2-B724-4E6C7232D62C}" name="MAX VAV_x000a_(CFM)" dataDxfId="33" totalsRowDxfId="14" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MAX SA(CFM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6A34627A-AFA3-4AC5-A2F5-3F20E11DD313}" name="VAV INLET SIZE_x000a_(IN)" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="5" xr3:uid="{404404D6-B6A1-4A11-B2D1-D270924F965F}" name="VAV INLET SIZE_x000a_(IN)" dataDxfId="32" totalsRowDxfId="13" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
 (CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{2249130A-E7BC-4C18-83FE-F02EB4556C4E}" name="MAX TOTAL VAV PD _x000a_(IN W.G.)" dataDxfId="25" totalsRowDxfId="24">
+    <tableColumn id="6" xr3:uid="{595BB365-8C94-434E-9DA5-22F5899737CD}" name="MAX TOTAL VAV PD _x000a_(IN W.G.)" dataDxfId="31" totalsRowDxfId="12" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>G4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{CE1C22EB-9A4A-4A1F-8C5C-19B6B06E4F7D}" name="HEATING AIRFLOW _x000a_(CFM)" dataDxfId="23" totalsRowDxfId="22">
+    <tableColumn id="19" xr3:uid="{4929FBB0-9F69-49AD-8474-3FB76AF65216}" name="HEATING AIRFLOW _x000a_(CFM)" dataDxfId="30" totalsRowDxfId="11" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>AH1_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A1F44238-8653-4F80-A833-797EB6F547FB}" name="EWT" dataDxfId="21" totalsRowDxfId="20">
+    <tableColumn id="7" xr3:uid="{D7CEB7B1-16A0-44D7-8021-26537126FF1E}" name="EWT" dataDxfId="29" totalsRowDxfId="10" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$16</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{B34647A2-B557-4694-9119-FEE1AA6523C5}" name="DESIGN _x000a_LWT" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="8" xr3:uid="{2754C70A-0BE7-49EF-ABB4-70F0D2E16A23}" name="DESIGN _x000a_LWT" dataDxfId="28" totalsRowDxfId="9" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$17</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C99192A1-C8CA-46F4-BECA-1A32119022DB}" name="EAT" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="9" xr3:uid="{050EE4BC-75A7-4F08-B96D-2070C39C239D}" name="EAT" dataDxfId="27" totalsRowDxfId="8" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>K4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{59911B13-CA65-432C-BD52-21DDCBE5B111}" name="DESIGN _x000a_LAT" dataDxfId="15" totalsRowDxfId="14">
+    <tableColumn id="10" xr3:uid="{8329506B-9326-4532-862F-5C8CFCF33C58}" name="DESIGN _x000a_LAT" dataDxfId="26" totalsRowDxfId="7" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>L4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{70C2E27D-762A-40F0-892D-DAB2251520E9}" name="MIN MBH" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="11" xr3:uid="{EFA26FC8-2332-45C3-9221-B2360BD518B7}" name="MIN MBH" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="6" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>MROUND((1.08*(L5-K5)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{01C8204D-DA57-4186-BCAE-6FC99CDD4A7C}" name="AGPM" dataDxfId="11" totalsRowDxfId="10">
+    <tableColumn id="12" xr3:uid="{51403382-CC86-4920-9FF2-88434A5DB79B}" name="AGPM" dataDxfId="24" totalsRowDxfId="5" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>(M5*1000)/(500*(I5-J5))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{77D26E95-5031-4CD3-BA42-2D1A68CFFBC3}" name="GPM" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="13" xr3:uid="{47868698-B0D7-4E5A-AE85-D43DC77ABD0F}" name="GPM" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="4" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>IF(N5&lt;0.5,0.5,N5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{487166D9-796A-4AB6-8E34-2527902449ED}" name="MAX WATER _x000a_PD (FT)" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="14" xr3:uid="{32CB265C-DCAD-4F2F-8A05-E71F6A4AD20F}" name="MAX WATER _x000a_PD (FT)" dataDxfId="22" totalsRowDxfId="3" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>P4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{F004DD6C-29A9-4BE7-A305-9D6CE72FC17A}" name="OPER _x000a_WEIGHT_x000a_(LBS)" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="15" xr3:uid="{642BF388-2DE1-4713-A96F-551DB0C45771}" name="OPER _x000a_WEIGHT_x000a_(LBS)" dataDxfId="21" totalsRowDxfId="2" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR((_xlfn.XLOOKUP(F5,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{71BA9FB3-160C-4ECB-A0C3-2C137D111764}" name="MTG _x000a_DETAIL" dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="16" xr3:uid="{CE1A1E7F-A6E2-406E-BB2F-7E83197E726E}" name="MTG _x000a_DETAIL" dataDxfId="20" totalsRowDxfId="1" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{F1C779CD-77B6-4847-983F-F9693FA60D03}" name="REMARKS" dataDxfId="1" totalsRowDxfId="0">
+    <tableColumn id="17" xr3:uid="{DC6D9DC0-9003-4385-AB10-A97D3FD3AB65}" name="REMARKS" dataDxfId="19" totalsRowDxfId="0" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>S4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2400,18 +2273,18 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A4" dT="2023-01-20T03:02:14.75" personId="{15E600FB-89F4-415C-AD33-71A53D824548}" id="{57AE57DA-4710-4B7A-B7AD-D13E0998DF44}">
+  <threadedComment ref="A4" dT="2023-01-20T03:02:14.75" personId="{5E313C26-8C82-4988-B6C0-99D50F1B0F4E}" id="{1CC13B16-4C20-403A-AC1C-35A7DA0101B2}">
     <text>Increase or decrease number of rows in this table to match the number of zones.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DD687A-F057-4252-B01A-16654A923520}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F309B6-F8DF-40DD-B96E-3A4B43207C79}">
   <sheetPr codeName="Sheet14">
     <tabColor rgb="FF0000FF"/>
   </sheetPr>
-  <dimension ref="A4:S17"/>
+  <dimension ref="A4:S7"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="2" bestFit="1" customWidth="1"/>
@@ -2507,11 +2380,11 @@
       </c>
       <c r="D5" s="4">
         <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
+        <v>3240</v>
       </c>
       <c r="E5" s="3">
         <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
+        <v>6900</v>
       </c>
       <c r="F5" s="5">
         <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
@@ -2524,7 +2397,7 @@
       <c r="H5" s="5">
         <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</f>
-        <v>4740</v>
+        <v>3240</v>
       </c>
       <c r="I5" s="5">
         <f>[1]INPUT_OUTPUTS!$C$16</f>
@@ -2543,15 +2416,15 @@
       <c r="M5" s="5">
         <f ca="1">MROUND((1.08*(L5-K5)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</f>
-        <v>128</v>
+        <v>87.5</v>
       </c>
       <c r="N5" s="6">
         <f ca="1">(M5*1000)/(500*(I5-J5))</f>
-        <v>8.5333333333333332</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="O5" s="6">
         <f ca="1">IF(N5&lt;0.5,0.5,N5)</f>
-        <v>8.5333333333333332</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="P5" s="6">
         <v>5</v>
@@ -2647,763 +2520,33 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E7" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F7" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I7" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J7" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K7" s="5">
-        <v>55</v>
-      </c>
-      <c r="L7" s="5">
-        <v>80</v>
-      </c>
-      <c r="M7" s="5">
-        <f ca="1">MROUND((1.08*(L7-K7)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N7" s="6">
-        <f t="shared" ref="N7:N16" ca="1" si="0">(M7*1000)/(500*(I7-J7))</f>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O7" s="6">
-        <f t="shared" ref="O7:O16" ca="1" si="1">IF(N7&lt;0.5,0.5,N7)</f>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P7" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q7" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F7,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R7" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E8" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F8" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H8" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I8" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J8" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K8" s="5">
-        <v>55</v>
-      </c>
-      <c r="L8" s="5">
-        <v>80</v>
-      </c>
-      <c r="M8" s="5">
-        <f ca="1">MROUND((1.08*(L8-K8)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N8" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O8" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P8" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F8,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R8" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E9" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F9" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I9" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J9" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K9" s="5">
-        <v>55</v>
-      </c>
-      <c r="L9" s="5">
-        <v>80</v>
-      </c>
-      <c r="M9" s="5">
-        <f ca="1">MROUND((1.08*(L9-K9)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N9" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O9" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P9" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F9,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R9" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E10" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F10" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I10" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J10" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K10" s="5">
-        <v>55</v>
-      </c>
-      <c r="L10" s="5">
-        <v>80</v>
-      </c>
-      <c r="M10" s="5">
-        <f ca="1">MROUND((1.08*(L10-K10)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N10" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O10" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P10" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F10,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R10" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E11" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F11" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I11" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J11" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K11" s="5">
-        <v>55</v>
-      </c>
-      <c r="L11" s="5">
-        <v>80</v>
-      </c>
-      <c r="M11" s="5">
-        <f ca="1">MROUND((1.08*(L11-K11)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N11" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O11" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P11" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F11,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R11" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E12" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F12" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I12" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J12" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K12" s="5">
-        <v>55</v>
-      </c>
-      <c r="L12" s="5">
-        <v>80</v>
-      </c>
-      <c r="M12" s="5">
-        <f ca="1">MROUND((1.08*(L12-K12)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N12" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O12" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P12" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F12,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R12" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E13" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F13" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I13" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J13" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K13" s="5">
-        <v>55</v>
-      </c>
-      <c r="L13" s="5">
-        <v>80</v>
-      </c>
-      <c r="M13" s="5">
-        <f ca="1">MROUND((1.08*(L13-K13)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N13" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O13" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P13" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q13" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F13,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R13" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E14" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F14" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H14" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I14" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J14" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K14" s="5">
-        <v>55</v>
-      </c>
-      <c r="L14" s="5">
-        <v>80</v>
-      </c>
-      <c r="M14" s="5">
-        <f ca="1">MROUND((1.08*(L14-K14)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N14" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O14" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P14" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F14,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R14" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E15" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F15" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I15" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J15" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K15" s="5">
-        <v>55</v>
-      </c>
-      <c r="L15" s="5">
-        <v>80</v>
-      </c>
-      <c r="M15" s="5">
-        <f ca="1">MROUND((1.08*(L15-K15)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N15" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O15" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P15" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F15,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R15" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>4740</v>
-      </c>
-      <c r="E16" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>8400</v>
-      </c>
-      <c r="F16" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
-(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="H16" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
-(CFM)]]</f>
-        <v>4740</v>
-      </c>
-      <c r="I16" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$16</f>
-        <v>140</v>
-      </c>
-      <c r="J16" s="5">
-        <f>[1]INPUT_OUTPUTS!$C$17</f>
-        <v>110</v>
-      </c>
-      <c r="K16" s="5">
-        <v>55</v>
-      </c>
-      <c r="L16" s="5">
-        <v>80</v>
-      </c>
-      <c r="M16" s="5">
-        <f ca="1">MROUND((1.08*(L16-K16)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
-(CFM)]])/1000,0.1)</f>
-        <v>128</v>
-      </c>
-      <c r="N16" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="O16" s="6">
-        <f t="shared" ca="1" si="1"/>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="P16" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q16" s="6">
-        <f ca="1">IFERROR((_xlfn.XLOOKUP(F16,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
-      </c>
-      <c r="R16" s="6">
-        <f>[1]INPUT_OUTPUTS!$C$19</f>
-        <v>0</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9">
         <f ca="1">SUBTOTAL(109,AH1_VAV_table[MIN MBH])</f>
-        <v>1408</v>
-      </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="10">
+        <v>87.5</v>
+      </c>
+      <c r="N7" s="9"/>
+      <c r="O7" s="10">
         <f ca="1">SUBTOTAL(109,AH1_VAV_table[GPM])</f>
-        <v>94.36666666666666</v>
-      </c>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="11"/>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3444,7 +2587,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{755E0A75-1461-4835-98D0-078F6AA866C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9D204D-BC52-4CFB-93D8-7D022F7D17A0}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>

--- a/VAV Schedules (Linked to AHU Psych).xlsx
+++ b/VAV Schedules (Linked to AHU Psych).xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git Projects\PsychroCalc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608EB19D-9E66-4804-8A5A-776C4A558557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B22CF4A-06A8-46C5-8F86-EF50D00A98B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{255CF481-9D8E-4326-9236-7F323F1440D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{723E3896-8EE3-4930-BC4B-2B609D23150B}"/>
   </bookViews>
   <sheets>
-    <sheet name="AH1_VAV_SCHEDULES" sheetId="2" r:id="rId1"/>
+    <sheet name="AH22_VAV_SCHEDULES" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <externalReferences>
@@ -57,10 +57,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={1CC13B16-4C20-403A-AC1C-35A7DA0101B2}</author>
+    <author>tc={3CBBAA8D-C30C-4DA8-B15F-D0FBCB6B6E5F}</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{1CC13B16-4C20-403A-AC1C-35A7DA0101B2}">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{3CBBAA8D-C30C-4DA8-B15F-D0FBCB6B6E5F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -186,6 +186,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -202,7 +203,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -328,7 +329,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{2BEF4A22-EF41-4147-BABC-84CF8CD79B60}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{1ACAAAED-CBA8-418D-8A83-9C4D91646FFD}"/>
   </cellStyles>
   <dxfs count="44">
     <dxf>
@@ -1712,7 +1713,7 @@
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{433A2705-7D24-45C4-BD22-182E6DDC0EDC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DD08B56-9308-4401-B242-37921E99A0B2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1770,17 +1771,19 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INPUT_OUTPUTS"/>
+      <sheetName val="Humidifier_Schedule"/>
       <sheetName val="AshraeTable4a"/>
       <sheetName val="CAV_SCHEDULES"/>
       <sheetName val="62.1_MULTI_ZONE"/>
       <sheetName val="VAV_SCHEDULES"/>
       <sheetName val="Room Temperature"/>
-      <sheetName val="AH1"/>
+      <sheetName val="AH11"/>
+      <sheetName val="AH22"/>
       <sheetName val="AHU_SCHEDULES"/>
       <sheetName val="62.1_SINGLE_ZONE"/>
-      <sheetName val="FCU_SCHEDULES"/>
       <sheetName val="CH_and_Boiler_Schedule "/>
       <sheetName val="Misc_Rooms"/>
+      <sheetName val="FCU_SCHEDULES"/>
       <sheetName val="ASHRAE Table"/>
       <sheetName val="UMC Table 4-A"/>
       <sheetName val="DO NOT TOUCH"/>
@@ -1814,7 +1817,9 @@
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
-      <sheetData sheetId="14">
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16">
         <row r="9">
           <cell r="C9">
             <v>1</v>
@@ -1889,66 +1894,66 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Rushikesh Patil" id="{5E313C26-8C82-4988-B6C0-99D50F1B0F4E}" userId="S::rdp352@nyu.edu::e20300c4-5136-4b7e-8e5f-b0b27a3a3193" providerId="AD"/>
+  <person displayName="Rushikesh Patil" id="{68495914-0FB7-4080-A2CF-61EBBE6CAF58}" userId="S::rdp352@nyu.edu::e20300c4-5136-4b7e-8e5f-b0b27a3a3193" providerId="AD"/>
 </personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0225CE1B-3CC1-45C3-BD85-3A7AD65EB02C}" name="AH1_VAV_table" displayName="AH1_VAV_table" ref="A4:S7" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42" totalsRowDxfId="41" headerRowBorderDxfId="39" tableBorderDxfId="40" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8279FCE9-3F95-473A-AD7D-A2A90CE42C4E}" name="AH22_VAV_table" displayName="AH22_VAV_table" ref="A4:S7" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42" totalsRowDxfId="41" headerRowBorderDxfId="39" tableBorderDxfId="40" totalsRowBorderDxfId="38">
   <autoFilter ref="A4:S6" xr:uid="{13D566E9-CE9D-4920-9557-440C01DE1A40}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{BDD53485-BD27-4C42-BCE6-4A791F13693B}" name="ZONE" totalsRowLabel="Total" dataDxfId="37" totalsRowDxfId="18" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{87D39EA5-B0A4-4FD0-8141-476AD3CFAF7B}" name="BASIS OF DESIGN _x000a_MANUFACTURER" dataDxfId="36" totalsRowDxfId="17" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{1F4067F0-0958-440B-887B-D04A70FA8DD0}" name="DESCRIPTION" dataDxfId="35" totalsRowDxfId="16" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="18" xr3:uid="{D0A6DBCB-AF09-4AFE-AC42-84877BED6114}" name="MIN VAV_x000a_(CFM)" dataDxfId="34" totalsRowDxfId="15" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MIN SA(CFM)])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{0F8211BB-6592-4DB2-BF37-2FCCBFF1133A}" name="ZONE" totalsRowLabel="Total" dataDxfId="37" totalsRowDxfId="18" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{71AA1749-FB1A-4C46-A186-C8AB05B9998D}" name="BASIS OF DESIGN _x000a_MANUFACTURER" dataDxfId="36" totalsRowDxfId="17" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{C0EFFF65-4244-46E6-B7EC-67312D92D33C}" name="DESCRIPTION" dataDxfId="35" totalsRowDxfId="16" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="18" xr3:uid="{3E553283-295C-4D3A-853F-A1647023D432}" name="MIN VAV_x000a_(CFM)" dataDxfId="34" totalsRowDxfId="15" totalsRowCellStyle="Normal 2">
+      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MIN SA(CFM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{352CF6FC-C856-4BE2-B724-4E6C7232D62C}" name="MAX VAV_x000a_(CFM)" dataDxfId="33" totalsRowDxfId="14" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MAX SA(CFM)])</calculatedColumnFormula>
+    <tableColumn id="20" xr3:uid="{0EC4B1C5-EE4F-49A1-AFAB-F0D730A91B13}" name="MAX VAV_x000a_(CFM)" dataDxfId="33" totalsRowDxfId="14" totalsRowCellStyle="Normal 2">
+      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MAX SA(CFM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{404404D6-B6A1-4A11-B2D1-D270924F965F}" name="VAV INLET SIZE_x000a_(IN)" dataDxfId="32" totalsRowDxfId="13" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+    <tableColumn id="5" xr3:uid="{3BB01EB1-12AE-4D27-AE65-FB1EDCE94B38}" name="VAV INLET SIZE_x000a_(IN)" dataDxfId="32" totalsRowDxfId="13" totalsRowCellStyle="Normal 2">
+      <calculatedColumnFormula>IFERROR((VLOOKUP(AH22_VAV_table[[#This Row],[MAX VAV
 (CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{595BB365-8C94-434E-9DA5-22F5899737CD}" name="MAX TOTAL VAV PD _x000a_(IN W.G.)" dataDxfId="31" totalsRowDxfId="12" totalsRowCellStyle="Normal 2">
+    <tableColumn id="6" xr3:uid="{FA5D450C-CC44-4854-8591-F4050BEDD53F}" name="MAX TOTAL VAV PD _x000a_(IN W.G.)" dataDxfId="31" totalsRowDxfId="12" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>G4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{4929FBB0-9F69-49AD-8474-3FB76AF65216}" name="HEATING AIRFLOW _x000a_(CFM)" dataDxfId="30" totalsRowDxfId="11" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>AH1_VAV_table[[#This Row],[MIN VAV
+    <tableColumn id="19" xr3:uid="{EAA26E7D-0EA4-49C5-9BE2-05921662B900}" name="HEATING AIRFLOW _x000a_(CFM)" dataDxfId="30" totalsRowDxfId="11" totalsRowCellStyle="Normal 2">
+      <calculatedColumnFormula>AH22_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D7CEB7B1-16A0-44D7-8021-26537126FF1E}" name="EWT" dataDxfId="29" totalsRowDxfId="10" totalsRowCellStyle="Normal 2">
+    <tableColumn id="7" xr3:uid="{2B680831-6A21-4B70-AB0D-EE9C984D1733}" name="EWT" dataDxfId="29" totalsRowDxfId="10" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$16</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{2754C70A-0BE7-49EF-ABB4-70F0D2E16A23}" name="DESIGN _x000a_LWT" dataDxfId="28" totalsRowDxfId="9" totalsRowCellStyle="Normal 2">
+    <tableColumn id="8" xr3:uid="{A4232F63-2191-47AB-861C-3A3E52CE45FA}" name="DESIGN _x000a_LWT" dataDxfId="28" totalsRowDxfId="9" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$17</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{050EE4BC-75A7-4F08-B96D-2070C39C239D}" name="EAT" dataDxfId="27" totalsRowDxfId="8" totalsRowCellStyle="Normal 2">
+    <tableColumn id="9" xr3:uid="{0F677DDF-2A8D-4E86-85A6-819352FB2116}" name="EAT" dataDxfId="27" totalsRowDxfId="8" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>K4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{8329506B-9326-4532-862F-5C8CFCF33C58}" name="DESIGN _x000a_LAT" dataDxfId="26" totalsRowDxfId="7" totalsRowCellStyle="Normal 2">
+    <tableColumn id="10" xr3:uid="{4D32D8CC-35BF-436D-8F23-561F3E62C915}" name="DESIGN _x000a_LAT" dataDxfId="26" totalsRowDxfId="7" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>L4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{EFA26FC8-2332-45C3-9221-B2360BD518B7}" name="MIN MBH" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="6" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>MROUND((1.08*(L5-K5)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+    <tableColumn id="11" xr3:uid="{D10A89FE-5913-43E9-83BC-A3CD3E0510C8}" name="MIN MBH" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="6" totalsRowCellStyle="Normal 2">
+      <calculatedColumnFormula>MROUND((1.08*(L5-K5)*AH22_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{51403382-CC86-4920-9FF2-88434A5DB79B}" name="AGPM" dataDxfId="24" totalsRowDxfId="5" totalsRowCellStyle="Normal 2">
+    <tableColumn id="12" xr3:uid="{662B8BE4-832D-40EA-A6CE-EACFD7B15578}" name="AGPM" dataDxfId="24" totalsRowDxfId="5" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>(M5*1000)/(500*(I5-J5))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{47868698-B0D7-4E5A-AE85-D43DC77ABD0F}" name="GPM" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="4" totalsRowCellStyle="Normal 2">
+    <tableColumn id="13" xr3:uid="{6D918336-D6F3-4F81-B8FC-CC94C4119F99}" name="GPM" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="4" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>IF(N5&lt;0.5,0.5,N5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{32CB265C-DCAD-4F2F-8A05-E71F6A4AD20F}" name="MAX WATER _x000a_PD (FT)" dataDxfId="22" totalsRowDxfId="3" totalsRowCellStyle="Normal 2">
+    <tableColumn id="14" xr3:uid="{11EEAAFD-867A-4132-BEC1-8C30F015A328}" name="MAX WATER _x000a_PD (FT)" dataDxfId="22" totalsRowDxfId="3" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>P4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{642BF388-2DE1-4713-A96F-551DB0C45771}" name="OPER _x000a_WEIGHT_x000a_(LBS)" dataDxfId="21" totalsRowDxfId="2" totalsRowCellStyle="Normal 2">
+    <tableColumn id="15" xr3:uid="{2AA0B1E4-A854-449E-B820-330493E6BF7D}" name="OPER _x000a_WEIGHT_x000a_(LBS)" dataDxfId="21" totalsRowDxfId="2" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>IFERROR((_xlfn.XLOOKUP(F5,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{CE1A1E7F-A6E2-406E-BB2F-7E83197E726E}" name="MTG _x000a_DETAIL" dataDxfId="20" totalsRowDxfId="1" totalsRowCellStyle="Normal 2">
+    <tableColumn id="16" xr3:uid="{94EBEA7D-FD89-42E9-871E-5FF81715A646}" name="MTG _x000a_DETAIL" dataDxfId="20" totalsRowDxfId="1" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{DC6D9DC0-9003-4385-AB10-A97D3FD3AB65}" name="REMARKS" dataDxfId="19" totalsRowDxfId="0" totalsRowCellStyle="Normal 2">
+    <tableColumn id="17" xr3:uid="{AD0439E6-4D78-4B59-9C36-4A7945F9C09F}" name="REMARKS" dataDxfId="19" totalsRowDxfId="0" totalsRowCellStyle="Normal 2">
       <calculatedColumnFormula>S4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2273,14 +2278,14 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A4" dT="2023-01-20T03:02:14.75" personId="{5E313C26-8C82-4988-B6C0-99D50F1B0F4E}" id="{1CC13B16-4C20-403A-AC1C-35A7DA0101B2}">
+  <threadedComment ref="A4" dT="2023-01-20T03:02:14.75" personId="{68495914-0FB7-4080-A2CF-61EBBE6CAF58}" id="{3CBBAA8D-C30C-4DA8-B15F-D0FBCB6B6E5F}">
     <text>Increase or decrease number of rows in this table to match the number of zones.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F309B6-F8DF-40DD-B96E-3A4B43207C79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228EF299-9A8A-465E-91FA-29FCD8611DA5}">
   <sheetPr codeName="Sheet14">
     <tabColor rgb="FF0000FF"/>
   </sheetPr>
@@ -2379,15 +2384,15 @@
         <v>21</v>
       </c>
       <c r="D5" s="4">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>3240</v>
+        <f ca="1">SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>3015</v>
       </c>
       <c r="E5" s="3">
-        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>6900</v>
+        <f ca="1">SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>6850</v>
       </c>
       <c r="F5" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+        <f ca="1">IFERROR((VLOOKUP(AH22_VAV_table[[#This Row],[MAX VAV
 (CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
         <v>16</v>
       </c>
@@ -2395,9 +2400,9 @@
         <v>0.5</v>
       </c>
       <c r="H5" s="5">
-        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+        <f ca="1">AH22_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</f>
-        <v>3240</v>
+        <v>3015</v>
       </c>
       <c r="I5" s="5">
         <f>[1]INPUT_OUTPUTS!$C$16</f>
@@ -2414,17 +2419,17 @@
         <v>80</v>
       </c>
       <c r="M5" s="5">
-        <f ca="1">MROUND((1.08*(L5-K5)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+        <f ca="1">MROUND((1.08*(L5-K5)*AH22_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</f>
-        <v>87.5</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="N5" s="6">
         <f ca="1">(M5*1000)/(500*(I5-J5))</f>
-        <v>5.833333333333333</v>
+        <v>5.4266666666666667</v>
       </c>
       <c r="O5" s="6">
         <f ca="1">IF(N5&lt;0.5,0.5,N5)</f>
-        <v>5.833333333333333</v>
+        <v>5.4266666666666667</v>
       </c>
       <c r="P5" s="6">
         <v>5</v>
@@ -2452,15 +2457,15 @@
         <v>21</v>
       </c>
       <c r="D6" s="4">
-        <f>SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <f>SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <f>SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <f>SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
         <v>0</v>
       </c>
       <c r="F6" s="5" t="str">
-        <f>IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+        <f>IFERROR((VLOOKUP(AH22_VAV_table[[#This Row],[MAX VAV
 (CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
         <v>TBD</v>
       </c>
@@ -2469,7 +2474,7 @@
         <v>0.5</v>
       </c>
       <c r="H6" s="5">
-        <f>AH1_VAV_table[[#This Row],[MIN VAV
+        <f>AH22_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</f>
         <v>0</v>
       </c>
@@ -2490,7 +2495,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5">
-        <f>MROUND((1.08*(L6-K6)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+        <f>MROUND((1.08*(L6-K6)*AH22_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</f>
         <v>0</v>
       </c>
@@ -2535,13 +2540,13 @@
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9">
-        <f ca="1">SUBTOTAL(109,AH1_VAV_table[MIN MBH])</f>
-        <v>87.5</v>
+        <f ca="1">SUBTOTAL(109,AH22_VAV_table[MIN MBH])</f>
+        <v>81.400000000000006</v>
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="10">
-        <f ca="1">SUBTOTAL(109,AH1_VAV_table[GPM])</f>
-        <v>6.333333333333333</v>
+        <f ca="1">SUBTOTAL(109,AH22_VAV_table[GPM])</f>
+        <v>5.9266666666666667</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -2587,8 +2592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D9D204D-BC52-4CFB-93D8-7D022F7D17A0}">
-  <sheetPr codeName="Sheet1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E117E373-8075-4B7A-97B1-96A4C46F27A2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>

--- a/VAV Schedules (Linked to AHU Psych).xlsx
+++ b/VAV Schedules (Linked to AHU Psych).xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git Projects\PsychroCalc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B22CF4A-06A8-46C5-8F86-EF50D00A98B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B90C051-37CF-4B7C-9579-ADE7C505F88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{723E3896-8EE3-4930-BC4B-2B609D23150B}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="25224" windowHeight="15372" xr2:uid="{FEA30A23-4686-4E04-97C6-A99903D72D45}"/>
   </bookViews>
   <sheets>
-    <sheet name="AH22_VAV_SCHEDULES" sheetId="2" r:id="rId1"/>
+    <sheet name="AH1_VAV_SCHEDULES" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <externalReferences>
@@ -32,6 +32,9 @@
     <definedName name="CAV_2_SCHEDULE">#REF!</definedName>
     <definedName name="CAV_3_SCHEDULE">#REF!</definedName>
     <definedName name="FCU">#REF!</definedName>
+    <definedName name="Space_air_rates">#REF!</definedName>
+    <definedName name="Space_index">#REF!</definedName>
+    <definedName name="VAV" localSheetId="0">AH1_VAV_table[[#All],[DESCRIPTION]:[REMARKS]]</definedName>
     <definedName name="VENTILATION_SCHEDULE_AHU_3">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -57,10 +60,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={3CBBAA8D-C30C-4DA8-B15F-D0FBCB6B6E5F}</author>
+    <author>tc={6FDB9193-F9C1-4957-B5F3-4D0863FD0B0F}</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{3CBBAA8D-C30C-4DA8-B15F-D0FBCB6B6E5F}">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{6FDB9193-F9C1-4957-B5F3-4D0863FD0B0F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -73,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="41">
   <si>
     <t>ZONE</t>
   </si>
@@ -160,6 +163,54 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>VAV-1-03</t>
+  </si>
+  <si>
+    <t>VAV-1-04</t>
+  </si>
+  <si>
+    <t>VAV-1-05</t>
+  </si>
+  <si>
+    <t>VAV-1-06</t>
+  </si>
+  <si>
+    <t>VAV-1-07</t>
+  </si>
+  <si>
+    <t>VAV-1-08</t>
+  </si>
+  <si>
+    <t>VAV-1-09</t>
+  </si>
+  <si>
+    <t>VAV-1-10</t>
+  </si>
+  <si>
+    <t>VAV-1-11</t>
+  </si>
+  <si>
+    <t>VAV-1-12</t>
+  </si>
+  <si>
+    <t>VAV-1-13</t>
+  </si>
+  <si>
+    <t>VAV-1-14</t>
+  </si>
+  <si>
+    <t>VAV-1-15</t>
+  </si>
+  <si>
+    <t>VAV-1-16</t>
+  </si>
+  <si>
+    <t>VAV-1-17</t>
+  </si>
+  <si>
+    <t>VAV-1-18</t>
   </si>
 </sst>
 </file>
@@ -200,10 +251,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -306,30 +357,30 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{1ACAAAED-CBA8-418D-8A83-9C4D91646FFD}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{561EB819-1ED4-4961-AE32-33B0788CA058}"/>
   </cellStyles>
   <dxfs count="44">
     <dxf>
@@ -349,6 +400,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -382,15 +440,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
+        <right/>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -411,38 +469,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -479,15 +512,17 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -508,6 +543,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -540,18 +582,21 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -572,6 +617,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -604,18 +656,21 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -636,6 +691,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -668,18 +730,21 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -700,6 +765,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -732,18 +804,21 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -764,6 +839,13 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -799,12 +881,53 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
           <color auto="1"/>
         </top>
         <bottom/>
@@ -823,11 +946,563 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -860,6 +1535,48 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -892,6 +1609,47 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -924,6 +1682,47 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -949,622 +1748,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
         <color theme="1"/>
         <name val="Arial"/>
         <family val="2"/>
@@ -1593,11 +1776,14 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1617,16 +1803,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1644,6 +1820,13 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1713,7 +1896,7 @@
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DD08B56-9308-4401-B242-37921E99A0B2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1777,13 +1960,14 @@
       <sheetName val="62.1_MULTI_ZONE"/>
       <sheetName val="VAV_SCHEDULES"/>
       <sheetName val="Room Temperature"/>
-      <sheetName val="AH11"/>
-      <sheetName val="AH22"/>
+      <sheetName val="AH1"/>
       <sheetName val="AHU_SCHEDULES"/>
       <sheetName val="62.1_SINGLE_ZONE"/>
+      <sheetName val="Title_24"/>
       <sheetName val="CH_and_Boiler_Schedule "/>
       <sheetName val="Misc_Rooms"/>
       <sheetName val="FCU_SCHEDULES"/>
+      <sheetName val="CALIFORNIA_TABLE"/>
       <sheetName val="ASHRAE Table"/>
       <sheetName val="UMC Table 4-A"/>
       <sheetName val="DO NOT TOUCH"/>
@@ -1819,7 +2003,8 @@
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
-      <sheetData sheetId="16">
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17">
         <row r="9">
           <cell r="C9">
             <v>1</v>
@@ -1894,66 +2079,66 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Rushikesh Patil" id="{68495914-0FB7-4080-A2CF-61EBBE6CAF58}" userId="S::rdp352@nyu.edu::e20300c4-5136-4b7e-8e5f-b0b27a3a3193" providerId="AD"/>
+  <person displayName="Rushikesh Patil" id="{C5CD77A2-A593-4389-852A-8A0614FACAE6}" userId="S::rdp352@nyu.edu::e20300c4-5136-4b7e-8e5f-b0b27a3a3193" providerId="AD"/>
 </personList>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8279FCE9-3F95-473A-AD7D-A2A90CE42C4E}" name="AH22_VAV_table" displayName="AH22_VAV_table" ref="A4:S7" totalsRowCount="1" headerRowDxfId="43" dataDxfId="42" totalsRowDxfId="41" headerRowBorderDxfId="39" tableBorderDxfId="40" totalsRowBorderDxfId="38">
-  <autoFilter ref="A4:S6" xr:uid="{13D566E9-CE9D-4920-9557-440C01DE1A40}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{290A3707-679C-44E1-8017-06867ABC8887}" name="AH1_VAV_table" displayName="AH1_VAV_table" ref="A4:S23" totalsRowCount="1" headerRowDxfId="43" dataDxfId="41" totalsRowDxfId="39" headerRowBorderDxfId="42" tableBorderDxfId="40" totalsRowBorderDxfId="38">
+  <autoFilter ref="A4:S22" xr:uid="{13D566E9-CE9D-4920-9557-440C01DE1A40}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{0F8211BB-6592-4DB2-BF37-2FCCBFF1133A}" name="ZONE" totalsRowLabel="Total" dataDxfId="37" totalsRowDxfId="18" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{71AA1749-FB1A-4C46-A186-C8AB05B9998D}" name="BASIS OF DESIGN _x000a_MANUFACTURER" dataDxfId="36" totalsRowDxfId="17" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{C0EFFF65-4244-46E6-B7EC-67312D92D33C}" name="DESCRIPTION" dataDxfId="35" totalsRowDxfId="16" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="18" xr3:uid="{3E553283-295C-4D3A-853F-A1647023D432}" name="MIN VAV_x000a_(CFM)" dataDxfId="34" totalsRowDxfId="15" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MIN SA(CFM)])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{8001F64A-B637-471E-874C-04B0F7C75127}" name="ZONE" totalsRowLabel="Total" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{A13F6D93-13F4-44AD-8158-8E5621C6E706}" name="BASIS OF DESIGN _x000a_MANUFACTURER" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{3309ECD7-ECC1-46D1-9C88-9144FF2DAD2D}" name="DESCRIPTION" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="18" xr3:uid="{D5F276E9-4CDD-4E56-A0D0-843320A8DEED}" name="MIN VAV_x000a_(CFM)" dataDxfId="31" totalsRowDxfId="30">
+      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MIN SA(CFM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{0EC4B1C5-EE4F-49A1-AFAB-F0D730A91B13}" name="MAX VAV_x000a_(CFM)" dataDxfId="33" totalsRowDxfId="14" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MAX SA(CFM)])</calculatedColumnFormula>
+    <tableColumn id="20" xr3:uid="{7DB37756-E803-4A82-87A4-F7ACFEF208C9}" name="MAX VAV_x000a_(CFM)" dataDxfId="29" totalsRowDxfId="28">
+      <calculatedColumnFormula>SUMIF([1]!Ahu_Ashrae_Generic[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!Ahu_Ashrae_Generic[DESIGN VAV MAX SA(CFM)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3BB01EB1-12AE-4D27-AE65-FB1EDCE94B38}" name="VAV INLET SIZE_x000a_(IN)" dataDxfId="32" totalsRowDxfId="13" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>IFERROR((VLOOKUP(AH22_VAV_table[[#This Row],[MAX VAV
+    <tableColumn id="5" xr3:uid="{1761E75F-D322-4793-B494-E2F4F59C30F9}" name="VAV INLET SIZE_x000a_(IN)" dataDxfId="27" totalsRowDxfId="26">
+      <calculatedColumnFormula>IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
 (CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{FA5D450C-CC44-4854-8591-F4050BEDD53F}" name="MAX TOTAL VAV PD _x000a_(IN W.G.)" dataDxfId="31" totalsRowDxfId="12" totalsRowCellStyle="Normal 2">
+    <tableColumn id="6" xr3:uid="{E891CC81-0240-4481-A65C-AB2E009EBC3C}" name="MAX TOTAL VAV PD _x000a_(IN W.G.)" dataDxfId="25" totalsRowDxfId="24">
       <calculatedColumnFormula>G4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{EAA26E7D-0EA4-49C5-9BE2-05921662B900}" name="HEATING AIRFLOW _x000a_(CFM)" dataDxfId="30" totalsRowDxfId="11" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>AH22_VAV_table[[#This Row],[MIN VAV
+    <tableColumn id="19" xr3:uid="{AAAA720B-5067-4F98-945B-A67D13E3FD53}" name="HEATING AIRFLOW _x000a_(CFM)" dataDxfId="23" totalsRowDxfId="22">
+      <calculatedColumnFormula>AH1_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{2B680831-6A21-4B70-AB0D-EE9C984D1733}" name="EWT" dataDxfId="29" totalsRowDxfId="10" totalsRowCellStyle="Normal 2">
+    <tableColumn id="7" xr3:uid="{0E470501-D3AA-4BA9-B05B-28F744D0A5AD}" name="EWT" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$16</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{A4232F63-2191-47AB-861C-3A3E52CE45FA}" name="DESIGN _x000a_LWT" dataDxfId="28" totalsRowDxfId="9" totalsRowCellStyle="Normal 2">
+    <tableColumn id="8" xr3:uid="{C77703F7-7CC4-44A9-AD25-ED2ECBD9003B}" name="DESIGN _x000a_LWT" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$17</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{0F677DDF-2A8D-4E86-85A6-819352FB2116}" name="EAT" dataDxfId="27" totalsRowDxfId="8" totalsRowCellStyle="Normal 2">
+    <tableColumn id="9" xr3:uid="{FFAF42B2-A09F-408D-8736-CCD6B6981540}" name="EAT" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>K4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{4D32D8CC-35BF-436D-8F23-561F3E62C915}" name="DESIGN _x000a_LAT" dataDxfId="26" totalsRowDxfId="7" totalsRowCellStyle="Normal 2">
+    <tableColumn id="10" xr3:uid="{B7202F19-57A6-4E7A-82F4-E7B0C5FA5ED1}" name="DESIGN _x000a_LAT" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>L4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D10A89FE-5913-43E9-83BC-A3CD3E0510C8}" name="MIN MBH" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="6" totalsRowCellStyle="Normal 2">
-      <calculatedColumnFormula>MROUND((1.08*(L5-K5)*AH22_VAV_table[[#This Row],[HEATING AIRFLOW 
+    <tableColumn id="11" xr3:uid="{83E4B17F-89B4-4A2D-839D-32C81A5C5464}" name="MIN MBH" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12">
+      <calculatedColumnFormula>MROUND((1.08*(L5-K5)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{662B8BE4-832D-40EA-A6CE-EACFD7B15578}" name="AGPM" dataDxfId="24" totalsRowDxfId="5" totalsRowCellStyle="Normal 2">
+    <tableColumn id="12" xr3:uid="{E67F4592-0ADC-43A3-A935-71EFDCD49C79}" name="AGPM" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>(M5*1000)/(500*(I5-J5))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{6D918336-D6F3-4F81-B8FC-CC94C4119F99}" name="GPM" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="4" totalsRowCellStyle="Normal 2">
+    <tableColumn id="13" xr3:uid="{4C81A281-F60B-4C9F-B280-E3F236142E0A}" name="GPM" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>IF(N5&lt;0.5,0.5,N5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{11EEAAFD-867A-4132-BEC1-8C30F015A328}" name="MAX WATER _x000a_PD (FT)" dataDxfId="22" totalsRowDxfId="3" totalsRowCellStyle="Normal 2">
+    <tableColumn id="14" xr3:uid="{FB6F9E15-C982-4CFA-AECB-9A2A9C7700B6}" name="MAX WATER _x000a_PD (FT)" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>P4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2AA0B1E4-A854-449E-B820-330493E6BF7D}" name="OPER _x000a_WEIGHT_x000a_(LBS)" dataDxfId="21" totalsRowDxfId="2" totalsRowCellStyle="Normal 2">
+    <tableColumn id="15" xr3:uid="{95275D6A-A6C7-43A9-B7AE-56EE9CAE0A1C}" name="OPER _x000a_WEIGHT_x000a_(LBS)" dataDxfId="5" totalsRowDxfId="4">
       <calculatedColumnFormula>IFERROR((_xlfn.XLOOKUP(F5,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{94EBEA7D-FD89-42E9-871E-5FF81715A646}" name="MTG _x000a_DETAIL" dataDxfId="20" totalsRowDxfId="1" totalsRowCellStyle="Normal 2">
+    <tableColumn id="16" xr3:uid="{EE4B9891-2CBF-433A-8EFF-1E86E8132927}" name="MTG _x000a_DETAIL" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>[1]INPUT_OUTPUTS!$C$19</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{AD0439E6-4D78-4B59-9C36-4A7945F9C09F}" name="REMARKS" dataDxfId="19" totalsRowDxfId="0" totalsRowCellStyle="Normal 2">
+    <tableColumn id="17" xr3:uid="{342214C0-4502-483E-BD54-EB32181B94F7}" name="REMARKS" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>S4</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2278,18 +2463,18 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A4" dT="2023-01-20T03:02:14.75" personId="{68495914-0FB7-4080-A2CF-61EBBE6CAF58}" id="{3CBBAA8D-C30C-4DA8-B15F-D0FBCB6B6E5F}">
+  <threadedComment ref="A4" dT="2023-01-20T03:02:14.75" personId="{C5CD77A2-A593-4389-852A-8A0614FACAE6}" id="{6FDB9193-F9C1-4957-B5F3-4D0863FD0B0F}">
     <text>Increase or decrease number of rows in this table to match the number of zones.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228EF299-9A8A-465E-91FA-29FCD8611DA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B44713F7-3045-4D78-84B6-D5DFF8428AE1}">
   <sheetPr codeName="Sheet14">
     <tabColor rgb="FF0000FF"/>
   </sheetPr>
-  <dimension ref="A4:S7"/>
+  <dimension ref="A4:S23"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="2" bestFit="1" customWidth="1"/>
@@ -2384,25 +2569,25 @@
         <v>21</v>
       </c>
       <c r="D5" s="4">
-        <f ca="1">SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>3015</v>
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>75</v>
       </c>
       <c r="E5" s="3">
-        <f ca="1">SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>6850</v>
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>250</v>
       </c>
       <c r="F5" s="5">
-        <f ca="1">IFERROR((VLOOKUP(AH22_VAV_table[[#This Row],[MAX VAV
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
 (CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G5" s="5">
         <v>0.5</v>
       </c>
       <c r="H5" s="5">
-        <f ca="1">AH22_VAV_table[[#This Row],[MIN VAV
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</f>
-        <v>3015</v>
+        <v>75</v>
       </c>
       <c r="I5" s="5">
         <f>[1]INPUT_OUTPUTS!$C$16</f>
@@ -2419,24 +2604,24 @@
         <v>80</v>
       </c>
       <c r="M5" s="5">
-        <f ca="1">MROUND((1.08*(L5-K5)*AH22_VAV_table[[#This Row],[HEATING AIRFLOW 
+        <f ca="1">MROUND((1.08*(L5-K5)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</f>
-        <v>81.400000000000006</v>
+        <v>2</v>
       </c>
       <c r="N5" s="6">
-        <f ca="1">(M5*1000)/(500*(I5-J5))</f>
-        <v>5.4266666666666667</v>
+        <f t="shared" ref="N5:N22" ca="1" si="0">(M5*1000)/(500*(I5-J5))</f>
+        <v>0.13333333333333333</v>
       </c>
       <c r="O5" s="6">
-        <f ca="1">IF(N5&lt;0.5,0.5,N5)</f>
-        <v>5.4266666666666667</v>
+        <f t="shared" ref="O5:O22" ca="1" si="1">IF(N5&lt;0.5,0.5,N5)</f>
+        <v>0.5</v>
       </c>
       <c r="P5" s="6">
         <v>5</v>
       </c>
       <c r="Q5" s="6">
         <f ca="1">IFERROR((_xlfn.XLOOKUP(F5,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="R5" s="6">
         <f>[1]INPUT_OUTPUTS!$C$19</f>
@@ -2457,26 +2642,26 @@
         <v>21</v>
       </c>
       <c r="D6" s="4">
-        <f>SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
-        <v>0</v>
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>165</v>
       </c>
       <c r="E6" s="3">
-        <f>SUMIF([1]!AH22_Ashrae_table[Zone],AH22_VAV_table[[#This Row],[ZONE]],[1]!AH22_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="str">
-        <f>IFERROR((VLOOKUP(AH22_VAV_table[[#This Row],[MAX VAV
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F6" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
 (CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
-        <v>TBD</v>
+        <v>8</v>
       </c>
       <c r="G6" s="5">
         <f>G5</f>
         <v>0.5</v>
       </c>
       <c r="H6" s="5">
-        <f>AH22_VAV_table[[#This Row],[MIN VAV
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
 (CFM)]]</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="I6" s="5">
         <f>[1]INPUT_OUTPUTS!$C$16</f>
@@ -2495,25 +2680,25 @@
         <v>80</v>
       </c>
       <c r="M6" s="5">
-        <f>MROUND((1.08*(L6-K6)*AH22_VAV_table[[#This Row],[HEATING AIRFLOW 
+        <f ca="1">MROUND((1.08*(L6-K6)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
 (CFM)]])/1000,0.1)</f>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" s="6">
-        <f>(M6*1000)/(500*(I6-J6))</f>
-        <v>0</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0.3</v>
       </c>
       <c r="O6" s="6">
-        <f>IF(N6&lt;0.5,0.5,N6)</f>
+        <f t="shared" ca="1" si="1"/>
         <v>0.5</v>
       </c>
       <c r="P6" s="6">
         <f>P5</f>
         <v>5</v>
       </c>
-      <c r="Q6" s="6" t="str">
-        <f>IFERROR((_xlfn.XLOOKUP(F6,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
-        <v>TBD</v>
+      <c r="Q6" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F6,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
       </c>
       <c r="R6" s="6">
         <f>[1]INPUT_OUTPUTS!$C$19</f>
@@ -2525,44 +2710,1214 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>165</v>
+      </c>
+      <c r="E7" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F7" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>165</v>
+      </c>
+      <c r="I7" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J7" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K7" s="5">
+        <v>55</v>
+      </c>
+      <c r="L7" s="5">
+        <v>80</v>
+      </c>
+      <c r="M7" s="5">
+        <f ca="1">MROUND((1.08*(L7-K7)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P7" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F7,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R7" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>165</v>
+      </c>
+      <c r="E8" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F8" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>165</v>
+      </c>
+      <c r="I8" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J8" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K8" s="5">
+        <v>55</v>
+      </c>
+      <c r="L8" s="5">
+        <v>80</v>
+      </c>
+      <c r="M8" s="5">
+        <f ca="1">MROUND((1.08*(L8-K8)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="N8" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P8" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F8,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R8" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>165</v>
+      </c>
+      <c r="E9" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F9" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>165</v>
+      </c>
+      <c r="I9" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J9" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K9" s="5">
+        <v>55</v>
+      </c>
+      <c r="L9" s="5">
+        <v>80</v>
+      </c>
+      <c r="M9" s="5">
+        <f ca="1">MROUND((1.08*(L9-K9)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P9" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F9,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R9" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>165</v>
+      </c>
+      <c r="E10" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F10" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>165</v>
+      </c>
+      <c r="I10" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J10" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K10" s="5">
+        <v>55</v>
+      </c>
+      <c r="L10" s="5">
+        <v>80</v>
+      </c>
+      <c r="M10" s="5">
+        <f ca="1">MROUND((1.08*(L10-K10)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P10" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F10,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R10" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>165</v>
+      </c>
+      <c r="E11" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F11" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>165</v>
+      </c>
+      <c r="I11" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J11" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K11" s="5">
+        <v>55</v>
+      </c>
+      <c r="L11" s="5">
+        <v>80</v>
+      </c>
+      <c r="M11" s="5">
+        <f ca="1">MROUND((1.08*(L11-K11)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>4.5</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P11" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F11,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R11" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>325</v>
+      </c>
+      <c r="E12" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F12" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>325</v>
+      </c>
+      <c r="I12" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J12" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K12" s="5">
+        <v>55</v>
+      </c>
+      <c r="L12" s="5">
+        <v>80</v>
+      </c>
+      <c r="M12" s="5">
+        <f ca="1">MROUND((1.08*(L12-K12)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="P12" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F12,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R12" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>325</v>
+      </c>
+      <c r="E13" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F13" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>325</v>
+      </c>
+      <c r="I13" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J13" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K13" s="5">
+        <v>55</v>
+      </c>
+      <c r="L13" s="5">
+        <v>80</v>
+      </c>
+      <c r="M13" s="5">
+        <f ca="1">MROUND((1.08*(L13-K13)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N13" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="O13" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="P13" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F13,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R13" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>325</v>
+      </c>
+      <c r="E14" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F14" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>325</v>
+      </c>
+      <c r="I14" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J14" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K14" s="5">
+        <v>55</v>
+      </c>
+      <c r="L14" s="5">
+        <v>80</v>
+      </c>
+      <c r="M14" s="5">
+        <f ca="1">MROUND((1.08*(L14-K14)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N14" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="O14" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="P14" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F14,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R14" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>325</v>
+      </c>
+      <c r="E15" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F15" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>325</v>
+      </c>
+      <c r="I15" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J15" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K15" s="5">
+        <v>55</v>
+      </c>
+      <c r="L15" s="5">
+        <v>80</v>
+      </c>
+      <c r="M15" s="5">
+        <f ca="1">MROUND((1.08*(L15-K15)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N15" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="O15" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="P15" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F15,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R15" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>325</v>
+      </c>
+      <c r="E16" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F16" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>325</v>
+      </c>
+      <c r="I16" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J16" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K16" s="5">
+        <v>55</v>
+      </c>
+      <c r="L16" s="5">
+        <v>80</v>
+      </c>
+      <c r="M16" s="5">
+        <f ca="1">MROUND((1.08*(L16-K16)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N16" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="O16" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="P16" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F16,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R16" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>325</v>
+      </c>
+      <c r="E17" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>550</v>
+      </c>
+      <c r="F17" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>8</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>325</v>
+      </c>
+      <c r="I17" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J17" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K17" s="5">
+        <v>55</v>
+      </c>
+      <c r="L17" s="5">
+        <v>80</v>
+      </c>
+      <c r="M17" s="5">
+        <f ca="1">MROUND((1.08*(L17-K17)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N17" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="O17" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.58666666666666667</v>
+      </c>
+      <c r="P17" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F17,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R17" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>75</v>
+      </c>
+      <c r="E18" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>250</v>
+      </c>
+      <c r="F18" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>6</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H18" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>75</v>
+      </c>
+      <c r="I18" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J18" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K18" s="5">
+        <v>55</v>
+      </c>
+      <c r="L18" s="5">
+        <v>80</v>
+      </c>
+      <c r="M18" s="5">
+        <f ca="1">MROUND((1.08*(L18-K18)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>2</v>
+      </c>
+      <c r="N18" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="O18" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P18" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F18,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R18" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>75</v>
+      </c>
+      <c r="E19" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>250</v>
+      </c>
+      <c r="F19" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>6</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>75</v>
+      </c>
+      <c r="I19" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J19" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K19" s="5">
+        <v>55</v>
+      </c>
+      <c r="L19" s="5">
+        <v>80</v>
+      </c>
+      <c r="M19" s="5">
+        <f ca="1">MROUND((1.08*(L19-K19)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>2</v>
+      </c>
+      <c r="N19" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="O19" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P19" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F19,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R19" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>75</v>
+      </c>
+      <c r="E20" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>250</v>
+      </c>
+      <c r="F20" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>6</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>75</v>
+      </c>
+      <c r="I20" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J20" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K20" s="5">
+        <v>55</v>
+      </c>
+      <c r="L20" s="5">
+        <v>80</v>
+      </c>
+      <c r="M20" s="5">
+        <f ca="1">MROUND((1.08*(L20-K20)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>2</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="O20" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F20,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R20" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>75</v>
+      </c>
+      <c r="E21" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>250</v>
+      </c>
+      <c r="F21" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>6</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>75</v>
+      </c>
+      <c r="I21" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J21" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K21" s="5">
+        <v>55</v>
+      </c>
+      <c r="L21" s="5">
+        <v>80</v>
+      </c>
+      <c r="M21" s="5">
+        <f ca="1">MROUND((1.08*(L21-K21)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>2</v>
+      </c>
+      <c r="N21" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="O21" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P21" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F21,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R21" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="4">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MIN SA(CFM)])</f>
+        <v>75</v>
+      </c>
+      <c r="E22" s="3">
+        <f ca="1">SUMIF([1]!AH1_Ashrae_table[Zone],AH1_VAV_table[[#This Row],[ZONE]],[1]!AH1_Ashrae_table[DESIGN VAV MAX SA(CFM)])</f>
+        <v>250</v>
+      </c>
+      <c r="F22" s="5">
+        <f ca="1">IFERROR((VLOOKUP(AH1_VAV_table[[#This Row],[MAX VAV
+(CFM)]],'[1]DO NOT TOUCH'!$C$9:$D$14,2,TRUE)),"TBD")</f>
+        <v>6</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="5">
+        <f ca="1">AH1_VAV_table[[#This Row],[MIN VAV
+(CFM)]]</f>
+        <v>75</v>
+      </c>
+      <c r="I22" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$16</f>
+        <v>140</v>
+      </c>
+      <c r="J22" s="5">
+        <f>[1]INPUT_OUTPUTS!$C$17</f>
+        <v>110</v>
+      </c>
+      <c r="K22" s="5">
+        <v>55</v>
+      </c>
+      <c r="L22" s="5">
+        <v>80</v>
+      </c>
+      <c r="M22" s="5">
+        <f ca="1">MROUND((1.08*(L22-K22)*AH1_VAV_table[[#This Row],[HEATING AIRFLOW 
+(CFM)]])/1000,0.1)</f>
+        <v>2</v>
+      </c>
+      <c r="N22" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="O22" s="6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="6">
+        <f ca="1">IFERROR((_xlfn.XLOOKUP(F22,'[1]DO NOT TOUCH'!$D$9:$D$14,'[1]DO NOT TOUCH'!$E$9:$E$14,)),"TBD")</f>
+        <v>30</v>
+      </c>
+      <c r="R22" s="6">
+        <f>[1]INPUT_OUTPUTS!$C$19</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9">
-        <f ca="1">SUBTOTAL(109,AH22_VAV_table[MIN MBH])</f>
-        <v>81.400000000000006</v>
-      </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="10">
-        <f ca="1">SUBTOTAL(109,AH22_VAV_table[GPM])</f>
-        <v>5.9266666666666667</v>
-      </c>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="11"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9">
+        <f ca="1">SUBTOTAL(109,AH1_VAV_table[MIN MBH])</f>
+        <v>91.799999999999983</v>
+      </c>
+      <c r="N23" s="9"/>
+      <c r="O23" s="10">
+        <f ca="1">SUBTOTAL(109,AH1_VAV_table[GPM])</f>
+        <v>9.5200000000000014</v>
+      </c>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="2049" r:id="rId3" name="Button 1">
+            <control shapeId="2049" r:id="rId4" name="Button 1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[1]!AddRowsToTableWithUserInput" altText="HUMIDIFICATION">
                 <anchor moveWithCells="1" sizeWithCells="1">
                   <from>
@@ -2586,13 +3941,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E117E373-8075-4B7A-97B1-96A4C46F27A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7324A7BA-1CEB-45AE-843E-AB35C1D3DEAD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
